--- a/data/output/2025/evaluasi_36.xlsx
+++ b/data/output/2025/evaluasi_36.xlsx
@@ -15,6 +15,7 @@
     <sheet name="3672" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="3673" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="3674" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3604" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1038,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1099,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.351104495356113</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5754056585323625</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.191991834064096</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.502332123672276</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1313,174 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3602</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.756648731726076</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3602</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.745372616756662</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3602</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.239999999999981</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3602</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3602</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6027956864820017</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3602</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebak</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.942072271901975</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1246,6 +1555,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.854213640816109</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.435324442084989</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.880412925999709</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8832799260990901</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.162865689205053</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5269181003253504</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1320,6 +1825,230 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-14.72041480709724</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.409170628217447</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.388514544142136</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6030217617972109</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2855806600113098</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4.625569993197474</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.099268100525735</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1334,7 +2063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,6 +2123,118 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.69181316070396</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.081050118901527</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.624438030511013</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1408,7 +2249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1552,6 +2393,118 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Serang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.53238204551316</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Serang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Serang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.067928945330155</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Serang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.321614962323269</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1566,7 +2519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1629,6 +2582,332 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.760000000000005</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.718272330588152</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.237680470402</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.939937545866369</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3604</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Serang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.965659886108477</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3604</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Serang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.740259999999997</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3604</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Serang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3604</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Serang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.528203285085253</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3604</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Serang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.5829030794088735</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
